--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -515,7 +515,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38d9e5d3-73a7-4e18-b3b9-aa1b26e4cc06}</x14:id>
+          <x14:id>{03126998-830b-4c6d-8a14-dff09b8f761c}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -529,7 +529,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0671ebad-2a52-43f6-a3a9-585018af6f01}</x14:id>
+          <x14:id>{2a93a170-0bdf-4e6c-8d83-14d933e7409d}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -543,7 +543,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b10551c-b4e0-4975-ac10-c045e09df4bf}</x14:id>
+          <x14:id>{ec910fde-fdb5-40e7-936b-ddae2eef85a2}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -557,7 +557,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49ad88bb-d5a9-4684-afcc-8033d8d051eb}</x14:id>
+          <x14:id>{e220e8c0-754c-49ee-b16c-50f15de1863c}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -571,7 +571,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93055e58-8649-4a74-9a8e-1e4036062ece}</x14:id>
+          <x14:id>{6d4bf625-187f-4815-83dc-28c8bfbe0ac6}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -585,7 +585,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{01b3b3bb-243e-4add-ae5b-fd208d5e5960}</x14:id>
+          <x14:id>{af040517-311e-4951-bd0d-fd7fce3f91aa}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -599,7 +599,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38d9e5d3-73a7-4e18-b3b9-aa1b26e4cc06}">
+          <x14:cfRule type="dataBar" id="{03126998-830b-4c6d-8a14-dff09b8f761c}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -610,7 +610,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0671ebad-2a52-43f6-a3a9-585018af6f01}">
+          <x14:cfRule type="dataBar" id="{2a93a170-0bdf-4e6c-8d83-14d933e7409d}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -625,7 +625,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0b10551c-b4e0-4975-ac10-c045e09df4bf}">
+          <x14:cfRule type="dataBar" id="{ec910fde-fdb5-40e7-936b-ddae2eef85a2}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -640,7 +640,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49ad88bb-d5a9-4684-afcc-8033d8d051eb}">
+          <x14:cfRule type="dataBar" id="{e220e8c0-754c-49ee-b16c-50f15de1863c}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -655,7 +655,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93055e58-8649-4a74-9a8e-1e4036062ece}">
+          <x14:cfRule type="dataBar" id="{6d4bf625-187f-4815-83dc-28c8bfbe0ac6}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -670,7 +670,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{01b3b3bb-243e-4add-ae5b-fd208d5e5960}">
+          <x14:cfRule type="dataBar" id="{af040517-311e-4951-bd0d-fd7fce3f91aa}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>

--- a/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
+++ b/XLibur.Tests/Resource/Examples/ConditionalFormatting/CFDataBars.xlsx
@@ -515,7 +515,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03126998-830b-4c6d-8a14-dff09b8f761c}</x14:id>
+          <x14:id>{f9c3d3c0-5f8c-4a6f-adb6-3635b1a2e329}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -529,7 +529,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a93a170-0bdf-4e6c-8d83-14d933e7409d}</x14:id>
+          <x14:id>{b62cf8c4-b196-42a2-9969-660980997667}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -543,7 +543,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec910fde-fdb5-40e7-936b-ddae2eef85a2}</x14:id>
+          <x14:id>{3a8f8f7a-a6c2-4b35-9264-856c9ed096dc}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -557,7 +557,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e220e8c0-754c-49ee-b16c-50f15de1863c}</x14:id>
+          <x14:id>{e63efefd-de5a-4b56-8e84-9ab2469077cd}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -571,7 +571,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d4bf625-187f-4815-83dc-28c8bfbe0ac6}</x14:id>
+          <x14:id>{3103f3ec-bcf3-4f5e-9ce6-034fe91a8a23}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -585,7 +585,7 @@
       </x:dataBar>
       <x:extLst>
         <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af040517-311e-4951-bd0d-fd7fce3f91aa}</x14:id>
+          <x14:id>{8c71b0ff-5a12-4137-9871-cb858ec8b916}</x14:id>
         </x:ext>
       </x:extLst>
     </x:cfRule>
@@ -599,7 +599,7 @@
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03126998-830b-4c6d-8a14-dff09b8f761c}">
+          <x14:cfRule type="dataBar" id="{f9c3d3c0-5f8c-4a6f-adb6-3635b1a2e329}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -610,7 +610,7 @@
           <xm:sqref>A2:A6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2a93a170-0bdf-4e6c-8d83-14d933e7409d}">
+          <x14:cfRule type="dataBar" id="{b62cf8c4-b196-42a2-9969-660980997667}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -625,7 +625,7 @@
           <xm:sqref>B2:B6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec910fde-fdb5-40e7-936b-ddae2eef85a2}">
+          <x14:cfRule type="dataBar" id="{3a8f8f7a-a6c2-4b35-9264-856c9ed096dc}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -640,7 +640,7 @@
           <xm:sqref>C2:C6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e220e8c0-754c-49ee-b16c-50f15de1863c}">
+          <x14:cfRule type="dataBar" id="{e63efefd-de5a-4b56-8e84-9ab2469077cd}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>50</xm:f>
@@ -655,7 +655,7 @@
           <xm:sqref>D2:D6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d4bf625-187f-4815-83dc-28c8bfbe0ac6}">
+          <x14:cfRule type="dataBar" id="{3103f3ec-bcf3-4f5e-9ce6-034fe91a8a23}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>-SUM($A$2:$E$2)</xm:f>
@@ -670,7 +670,7 @@
           <xm:sqref>E2:E6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af040517-311e-4951-bd0d-fd7fce3f91aa}">
+          <x14:cfRule type="dataBar" id="{8c71b0ff-5a12-4137-9871-cb858ec8b916}">
             <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
               <x14:cfvo type="num">
                 <xm:f>30</xm:f>
